--- a/artfynd/A 889-2026 artfynd.xlsx
+++ b/artfynd/A 889-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120274332</v>
+        <v>113650438</v>
       </c>
       <c r="B2" t="n">
-        <v>96946</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97975</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -727,14 +722,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gunneby, 800 m OSO Kållekärr centrum, Boh</t>
+          <t>Kållekärr, 300 m OSO vattentorn, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>303542</v>
+        <v>303410</v>
       </c>
       <c r="R2" t="n">
-        <v>6436042</v>
+        <v>6436033</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -761,17 +756,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2023-11-24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2023-11-24</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Hällmark. ( H. europaea enl. Björk 2000 )</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,6 +791,125 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>120274332</v>
+      </c>
+      <c r="B3" t="n">
+        <v>97975</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>224361</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Äkta lopplummer</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Huperzia europaea</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Gunneby, 800 m OSO Kållekärr centrum, Boh</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>303542</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6436042</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Tjörn</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Stig Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Stig Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
